--- a/Sample_run/1/student/dungtdhe186461/TC2/GradeDetail.xlsx
+++ b/Sample_run/1/student/dungtdhe186461/TC2/GradeDetail.xlsx
@@ -1044,7 +1044,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>38066</x:v>
+        <x:v>54508</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>38066</x:v>
+        <x:v>54508</x:v>
       </x:c>
       <x:c r="R5" s="4" t="s">
         <x:v>56</x:v>
